--- a/data_noidan.xlsx
+++ b/data_noidan.xlsx
@@ -3288,6 +3288,9 @@
       </c>
     </row>
     <row r="24" ht="63" customHeight="1" spans="1:8">
+      <c r="B24">
+        <v>6</v>
+      </c>
       <c r="D24" s="3" t="s">
         <v>65</v>
       </c>
@@ -3302,6 +3305,9 @@
       </c>
     </row>
     <row r="25" ht="63" customHeight="1" spans="1:8">
+      <c r="B25">
+        <v>7</v>
+      </c>
       <c r="D25" s="3" t="s">
         <v>67</v>
       </c>
@@ -3316,6 +3322,9 @@
       </c>
     </row>
     <row r="26" ht="63" customHeight="1" spans="1:8">
+      <c r="B26">
+        <v>8</v>
+      </c>
       <c r="D26" s="3" t="s">
         <v>70</v>
       </c>
